--- a/R/data/Final_Records_AR_2502_1220.xlsx
+++ b/R/data/Final_Records_AR_2502_1220.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kwlee/Documents/class202501/R/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B826D3F2-22DE-4F45-8528-04F65402A661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE6EE80-A6EE-8544-9596-3D80EDD039F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="44800" windowHeight="22720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
